--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.69936101425071</v>
+        <v>4.663646164815741</v>
       </c>
       <c r="D2" t="n">
-        <v>28.67069994856364</v>
+        <v>4.658988741641592</v>
       </c>
       <c r="E2" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F2" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.41209156570411</v>
+        <v>2.991964879426919</v>
       </c>
       <c r="D3" t="n">
-        <v>18.43342486017227</v>
+        <v>2.995431539777995</v>
       </c>
       <c r="E3" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F3" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.711474703219054</v>
+        <v>1.578114639273096</v>
       </c>
       <c r="D4" t="n">
-        <v>9.628131856366513</v>
+        <v>1.564571426659559</v>
       </c>
       <c r="E4" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F4" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.78277140486755</v>
+        <v>5.002200353290977</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67462679655085</v>
+        <v>4.984626854439513</v>
       </c>
       <c r="E5" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F5" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.05786384385405</v>
+        <v>4.721902874626283</v>
       </c>
       <c r="D6" t="n">
-        <v>29.01181353489659</v>
+        <v>4.714419699420695</v>
       </c>
       <c r="E6" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F6" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.6609591398875</v>
+        <v>5.469905860231719</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77639413364952</v>
+        <v>5.488664046718047</v>
       </c>
       <c r="E7" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F7" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.89173479692598</v>
+        <v>4.694906904500471</v>
       </c>
       <c r="D8" t="n">
-        <v>28.88695203370257</v>
+        <v>4.694129705476668</v>
       </c>
       <c r="E8" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F8" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95827378038613</v>
+        <v>4.543219489312746</v>
       </c>
       <c r="D9" t="n">
-        <v>28.05670427802637</v>
+        <v>4.559214445179285</v>
       </c>
       <c r="E9" t="n">
-        <v>7.358723398747363</v>
+        <v>1.195792552296446</v>
       </c>
       <c r="F9" t="n">
-        <v>7.38487500984586</v>
+        <v>1.200042189099952</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
